--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -583,7 +583,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>7.2686</v>
+        <v>7.8632</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -615,7 +615,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.3417</v>
+        <v>0.2767</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -623,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>2.9021</v>
+        <v>3.2354</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -631,7 +631,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>2.5603</v>
+        <v>2.9587</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -639,7 +639,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3.2438</v>
+        <v>3.5121</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -511,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -519,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -527,7 +527,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -551,7 +551,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -559,7 +559,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -591,7 +591,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>7.8632</v>
+        <v>8.735300000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -615,7 +615,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.2767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -623,7 +623,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>3.2354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -631,7 +631,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>2.9587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -639,7 +639,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>3.5121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -647,7 +647,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -655,7 +655,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -671,7 +671,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>5.0305</v>
+        <v>5.3357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -679,7 +679,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>5.1163</v>
+        <v>5.3927</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>3.0928</v>
+        <v>2.6442</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -695,7 +695,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.1112</v>
+        <v>0.8436</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -703,7 +703,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="29" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -583,7 +583,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>8.735300000000001</v>
+        <v>8.719799999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>8.719799999999999</v>
+        <v>8.4529</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>8.4529</v>
+        <v>9.0989</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/outputs/Block5B_Senate_Attribution_Summary.xlsx
+++ b/outputs/Block5B_Senate_Attribution_Summary.xlsx
@@ -559,7 +559,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -583,7 +583,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -599,7 +599,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -607,7 +607,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>9.0989</v>
+        <v>8.7857</v>
       </c>
     </row>
     <row r="17" spans="1:2">
